--- a/Funding_impactAnalysis/data/Sub_counties_mixed_tableHIVSyphilsdualkit.xlsx
+++ b/Funding_impactAnalysis/data/Sub_counties_mixed_tableHIVSyphilsdualkit.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">County</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub_county</t>
+    <t xml:space="preserve">Sub county</t>
   </si>
   <si>
     <t xml:space="preserve">Trend_Prepolicy (IRR)</t>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Kisumu </t>
   </si>
   <si>
-    <t xml:space="preserve">Seme</t>
+    <t xml:space="preserve">seme</t>
   </si>
   <si>
     <t xml:space="preserve">0.98</t>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">Siaya </t>
   </si>
   <si>
-    <t xml:space="preserve">Gem</t>
+    <t xml:space="preserve">gem</t>
   </si>
   <si>
     <t xml:space="preserve">2.08</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">Machakos </t>
   </si>
   <si>
-    <t xml:space="preserve">Athi River</t>
+    <t xml:space="preserve">mavoko</t>
   </si>
   <si>
     <t xml:space="preserve">Uasin Gishu </t>
   </si>
   <si>
-    <t xml:space="preserve">Ainabkoi</t>
+    <t xml:space="preserve">ainabkoi</t>
   </si>
   <si>
     <t xml:space="preserve">2.05</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">Kakamega </t>
   </si>
   <si>
-    <t xml:space="preserve">Butere</t>
+    <t xml:space="preserve">butere</t>
   </si>
   <si>
     <t xml:space="preserve">2.02</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Migori </t>
   </si>
   <si>
-    <t xml:space="preserve">Suna West</t>
+    <t xml:space="preserve">suna west</t>
   </si>
   <si>
     <t xml:space="preserve">2.01</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">Mombasa </t>
   </si>
   <si>
-    <t xml:space="preserve">Likoni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikolomani</t>
+    <t xml:space="preserve">likoni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ikolomani</t>
   </si>
   <si>
     <t xml:space="preserve">2.00</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapseret</t>
+    <t xml:space="preserve">kapseret</t>
   </si>
   <si>
     <t xml:space="preserve">Busia </t>
   </si>
   <si>
-    <t xml:space="preserve">Matayos</t>
+    <t xml:space="preserve">matayos</t>
   </si>
   <si>
     <t xml:space="preserve">1.99</t>
@@ -107,31 +107,31 @@
     <t xml:space="preserve">Kajiado </t>
   </si>
   <si>
-    <t xml:space="preserve">Kajiado Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uriri</t>
+    <t xml:space="preserve">kajiado central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uriri</t>
   </si>
   <si>
     <t xml:space="preserve">Bungoma </t>
   </si>
   <si>
-    <t xml:space="preserve">Cheptais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyatike</t>
+    <t xml:space="preserve">cheptais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyatike</t>
   </si>
   <si>
     <t xml:space="preserve">Elgeyo Marakwet </t>
   </si>
   <si>
-    <t xml:space="preserve">Keiyo North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alego Usonga</t>
+    <t xml:space="preserve">keiyo north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alego usonga</t>
   </si>
   <si>
     <t xml:space="preserve">1.98</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">Trans Nzoia </t>
   </si>
   <si>
-    <t xml:space="preserve">Cherangany</t>
+    <t xml:space="preserve">cherangany</t>
   </si>
   <si>
     <t xml:space="preserve">Kilifi </t>
   </si>
   <si>
-    <t xml:space="preserve">Kilifi South</t>
+    <t xml:space="preserve">kilifi south</t>
   </si>
   <si>
     <t xml:space="preserve">Nairobi </t>
   </si>
   <si>
-    <t xml:space="preserve">Westlands</t>
+    <t xml:space="preserve">westlands</t>
   </si>
   <si>
     <t xml:space="preserve">1.97</t>
   </si>
   <si>
-    <t xml:space="preserve">Saboti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malava</t>
+    <t xml:space="preserve">saboti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malava</t>
   </si>
   <si>
     <t xml:space="preserve">Kericho </t>
   </si>
   <si>
-    <t xml:space="preserve">Bureti</t>
+    <t xml:space="preserve">buret</t>
   </si>
   <si>
     <t xml:space="preserve">1.96</t>
@@ -176,52 +176,52 @@
     <t xml:space="preserve">Nakuru </t>
   </si>
   <si>
-    <t xml:space="preserve">Nakuru West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suna East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuresoi North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molo</t>
+    <t xml:space="preserve">nakuru town west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suna east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuresoi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molo</t>
   </si>
   <si>
     <t xml:space="preserve">1.95</t>
   </si>
   <si>
-    <t xml:space="preserve">Matungu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kadibo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Butula</t>
+    <t xml:space="preserve">matungu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kadibo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">butula</t>
   </si>
   <si>
     <t xml:space="preserve">Kitui </t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kasarani</t>
+    <t xml:space="preserve">kitui west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kasarani</t>
   </si>
   <si>
     <t xml:space="preserve">Turkana </t>
   </si>
   <si>
-    <t xml:space="preserve">Lokichoggio</t>
+    <t xml:space="preserve">lokichoggio</t>
   </si>
   <si>
     <t xml:space="preserve">Bomet </t>
   </si>
   <si>
-    <t xml:space="preserve">Sotik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magarini</t>
+    <t xml:space="preserve">sotik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magarini</t>
   </si>
   <si>
     <t xml:space="preserve">1.94</t>
@@ -230,565 +230,565 @@
     <t xml:space="preserve">Homa Bay </t>
   </si>
   <si>
-    <t xml:space="preserve">Suba South</t>
+    <t xml:space="preserve">suba south</t>
   </si>
   <si>
     <t xml:space="preserve">Marsabit </t>
   </si>
   <si>
-    <t xml:space="preserve">North Horr</t>
+    <t xml:space="preserve">north horr</t>
   </si>
   <si>
     <t xml:space="preserve">Kisii </t>
   </si>
   <si>
-    <t xml:space="preserve">South Mugirango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kajiado East</t>
+    <t xml:space="preserve">south mugirango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kajiado east</t>
   </si>
   <si>
     <t xml:space="preserve">1.93</t>
   </si>
   <si>
-    <t xml:space="preserve">Kisumu West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endebess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bondo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aroo</t>
+    <t xml:space="preserve">kisumu west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endebess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aroo</t>
   </si>
   <si>
     <t xml:space="preserve">1.92</t>
   </si>
   <si>
-    <t xml:space="preserve">Ugunja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi Central</t>
+    <t xml:space="preserve">ugunja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi central</t>
   </si>
   <si>
     <t xml:space="preserve">Vihiga </t>
   </si>
   <si>
-    <t xml:space="preserve">Emuhaya</t>
+    <t xml:space="preserve">emuhaya</t>
   </si>
   <si>
     <t xml:space="preserve">Baringo </t>
   </si>
   <si>
-    <t xml:space="preserve">Marigat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruaraka</t>
+    <t xml:space="preserve">marigat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruaraka</t>
   </si>
   <si>
     <t xml:space="preserve">1.91</t>
   </si>
   <si>
-    <t xml:space="preserve">Navakholo</t>
+    <t xml:space="preserve">navakholo</t>
   </si>
   <si>
     <t xml:space="preserve">Tharaka Nithi </t>
   </si>
   <si>
-    <t xml:space="preserve">Tharaka North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sirisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwanza</t>
+    <t xml:space="preserve">tharaka north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kisumu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sirisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kwanza</t>
   </si>
   <si>
     <t xml:space="preserve">1.90</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakuru North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lurambi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changamwe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rarieda</t>
+    <t xml:space="preserve">nakuru north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lurambi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">changamwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rarieda</t>
   </si>
   <si>
     <t xml:space="preserve">Taita Taveta </t>
   </si>
   <si>
-    <t xml:space="preserve">Voi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dagoretti South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi Central</t>
+    <t xml:space="preserve">voi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dagoretti south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi central</t>
   </si>
   <si>
     <t xml:space="preserve">1.89</t>
   </si>
   <si>
-    <t xml:space="preserve">Nambale</t>
+    <t xml:space="preserve">nambale</t>
   </si>
   <si>
     <t xml:space="preserve">Nandi </t>
   </si>
   <si>
-    <t xml:space="preserve">Mosop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwatate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sabatia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilifi North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachuonyo East</t>
+    <t xml:space="preserve">mosop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwatate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sabatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilifi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rachuonyo east</t>
   </si>
   <si>
     <t xml:space="preserve">Kirinyaga </t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webuye East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana South</t>
+    <t xml:space="preserve">kirinyaga central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">webuye east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana south</t>
   </si>
   <si>
     <t xml:space="preserve">1.88</t>
   </si>
   <si>
-    <t xml:space="preserve">Shinyalu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starehe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ainamoi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kipkelion West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamisi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiminini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kesses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugenya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamukunji</t>
+    <t xml:space="preserve">shinyalu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">starehe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ainamoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kipkelion west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hamisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiminini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kesses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ugenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamukunji</t>
   </si>
   <si>
     <t xml:space="preserve">1.87</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitutu Chache North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malindi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomet East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rongo</t>
+    <t xml:space="preserve">aldai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitutu chache north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malindi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomet east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rongo</t>
   </si>
   <si>
     <t xml:space="preserve">Embu </t>
   </si>
   <si>
-    <t xml:space="preserve">Mbeere North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vihiga</t>
+    <t xml:space="preserve">mbeere north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vihiga</t>
   </si>
   <si>
     <t xml:space="preserve">1.86</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitutu Chache South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyaribari Chache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyando</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomet Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baringo North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhoroni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonchari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bunyala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embu west</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuria East</t>
+    <t xml:space="preserve">kitutu chache south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyaribari chache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomet central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baringo north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muhoroni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bonchari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bunyala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embu west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuria east</t>
   </si>
   <si>
     <t xml:space="preserve">Nyandarua </t>
   </si>
   <si>
-    <t xml:space="preserve">Kinangop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Awendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuria West</t>
+    <t xml:space="preserve">kinangop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">awendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuria west</t>
   </si>
   <si>
     <t xml:space="preserve">1.85</t>
   </si>
   <si>
-    <t xml:space="preserve">Tinderet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likuyani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rongai</t>
+    <t xml:space="preserve">tinderet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">likuyani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rongai</t>
   </si>
   <si>
     <t xml:space="preserve">Meru </t>
   </si>
   <si>
-    <t xml:space="preserve">Tigania West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui Central</t>
+    <t xml:space="preserve">tigania west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui central</t>
   </si>
   <si>
     <t xml:space="preserve">1.84</t>
   </si>
   <si>
-    <t xml:space="preserve">Bumula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyaribari Masaba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marakwet West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olkalou</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matungulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suba North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mumias West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakuru East</t>
+    <t xml:space="preserve">bumula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyaribari masaba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marakwet west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ol kalou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matungulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suba north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mumias west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nakuru town east</t>
   </si>
   <si>
     <t xml:space="preserve">1.83</t>
   </si>
   <si>
-    <t xml:space="preserve">Jomvu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subukia</t>
+    <t xml:space="preserve">jomvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subukia</t>
   </si>
   <si>
     <t xml:space="preserve">Samburu </t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naivasha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomachoge Chache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Njoro</t>
+    <t xml:space="preserve">samburu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naivasha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomachoge chache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">njoro</t>
   </si>
   <si>
     <t xml:space="preserve">Laikipia </t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia West</t>
+    <t xml:space="preserve">laikipia west</t>
   </si>
   <si>
     <t xml:space="preserve">Kiambu </t>
   </si>
   <si>
-    <t xml:space="preserve">Githunguri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana Central</t>
+    <t xml:space="preserve">githunguri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana central</t>
   </si>
   <si>
     <t xml:space="preserve">1.82</t>
   </si>
   <si>
-    <t xml:space="preserve">Roysambu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kikuyu</t>
+    <t xml:space="preserve">roysambu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kikuyu</t>
   </si>
   <si>
     <t xml:space="preserve">Makueni </t>
   </si>
   <si>
-    <t xml:space="preserve">Makueni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui Rural</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laikipia East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loitokitok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachuonyo North </t>
+    <t xml:space="preserve">makueni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui rural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laikipia east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loitokitok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rachuonyo north</t>
   </si>
   <si>
     <t xml:space="preserve">1.81</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gilgil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baringo Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chuka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igembe North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganze</t>
+    <t xml:space="preserve">samburu north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gilgil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baringo central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mathare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chuka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">igembe north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ganze</t>
   </si>
   <si>
     <t xml:space="preserve">1.80</t>
   </si>
   <si>
-    <t xml:space="preserve">Teso South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kangundo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embu North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marakwet East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga North/Mwea West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khwisero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chepalungu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kajiado North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imenti Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chesumei</t>
+    <t xml:space="preserve">teso south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kangundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embu north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marakwet east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga north/mwea west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khwisero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chepalungu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kajiado north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cental imenti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chesumei</t>
   </si>
   <si>
     <t xml:space="preserve">1.79</t>
   </si>
   <si>
-    <t xml:space="preserve">Kalama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rabai</t>
+    <t xml:space="preserve">kalama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kisumu east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rabai</t>
   </si>
   <si>
     <t xml:space="preserve">Narok </t>
   </si>
   <si>
-    <t xml:space="preserve">Narok Central</t>
+    <t xml:space="preserve">narok central</t>
   </si>
   <si>
     <t xml:space="preserve">1.78</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaiti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaloleni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yatta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emgwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konoin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi West</t>
+    <t xml:space="preserve">kaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kaloleni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yatta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emgwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">konoin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi west</t>
   </si>
   <si>
     <t xml:space="preserve">1.77</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oljoroorok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu East</t>
+    <t xml:space="preserve">mwala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ol jorok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu east</t>
   </si>
   <si>
     <t xml:space="preserve">1.76</t>
   </si>
   <si>
-    <t xml:space="preserve">Maara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teso Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mbeere South</t>
+    <t xml:space="preserve">maara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teso central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mbeere south</t>
   </si>
   <si>
     <t xml:space="preserve">1.74</t>
   </si>
   <si>
-    <t xml:space="preserve">Machakos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabuchai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laikipia North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanduyi</t>
+    <t xml:space="preserve">machakos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kabuchai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laikipia north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kanduyi</t>
   </si>
   <si>
     <t xml:space="preserve">1.73</t>
   </si>
   <si>
-    <t xml:space="preserve">Igambangombe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kimilili</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muthambi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mvita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndaragwa</t>
+    <t xml:space="preserve">igambangombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kimilili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muthambi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
     <t xml:space="preserve">1.72</t>
   </si>
   <si>
-    <t xml:space="preserve">Mt Elgon</t>
+    <t xml:space="preserve">mt. elgon</t>
   </si>
   <si>
     <t xml:space="preserve">1.71</t>
   </si>
   <si>
-    <t xml:space="preserve">Masinga</t>
+    <t xml:space="preserve">masinga</t>
   </si>
   <si>
     <t xml:space="preserve">1.70</t>

--- a/Funding_impactAnalysis/data/Sub_counties_mixed_tableHIVSyphilsdualkit.xlsx
+++ b/Funding_impactAnalysis/data/Sub_counties_mixed_tableHIVSyphilsdualkit.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t xml:space="preserve">County</t>
   </si>
@@ -23,10 +23,10 @@
     <t xml:space="preserve">Trend_Prepolicy (IRR)</t>
   </si>
   <si>
-    <t xml:space="preserve">Level effect (IRR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu </t>
+    <t xml:space="preserve">IRR for Immediate effect (95% CI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kisumu</t>
   </si>
   <si>
     <t xml:space="preserve">seme</t>
@@ -35,97 +35,118 @@
     <t xml:space="preserve">0.98</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siaya </t>
+    <t xml:space="preserve">2.15 (1.45-3.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siaya</t>
   </si>
   <si>
     <t xml:space="preserve">gem</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machakos </t>
+    <t xml:space="preserve">2.08 (1.47-2.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machakos</t>
   </si>
   <si>
     <t xml:space="preserve">mavoko</t>
   </si>
   <si>
-    <t xml:space="preserve">Uasin Gishu </t>
+    <t xml:space="preserve">2.08 (1.46-2.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uasin Gishu</t>
   </si>
   <si>
     <t xml:space="preserve">ainabkoi</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kakamega </t>
+    <t xml:space="preserve">2.05 (1.47-2.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakamega</t>
   </si>
   <si>
     <t xml:space="preserve">butere</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migori </t>
+    <t xml:space="preserve">2.02 (1.47-2.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migori</t>
   </si>
   <si>
     <t xml:space="preserve">suna west</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mombasa </t>
+    <t xml:space="preserve">2.01 (1.47-2.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mombasa</t>
   </si>
   <si>
     <t xml:space="preserve">likoni</t>
   </si>
   <si>
+    <t xml:space="preserve">2.01 (1.46-2.76)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ikolomani</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00</t>
+    <t xml:space="preserve">2.00 (1.47-2.72)</t>
   </si>
   <si>
     <t xml:space="preserve">kapseret</t>
   </si>
   <si>
-    <t xml:space="preserve">Busia </t>
+    <t xml:space="preserve">2.00 (1.46-2.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busia</t>
   </si>
   <si>
     <t xml:space="preserve">matayos</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kajiado </t>
+    <t xml:space="preserve">1.99 (1.46-2.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kajiado</t>
   </si>
   <si>
     <t xml:space="preserve">kajiado central</t>
   </si>
   <si>
+    <t xml:space="preserve">1.99 (1.47-2.71)</t>
+  </si>
+  <si>
     <t xml:space="preserve">uriri</t>
   </si>
   <si>
-    <t xml:space="preserve">Bungoma </t>
+    <t xml:space="preserve">1.99 (1.47-2.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bungoma</t>
   </si>
   <si>
     <t xml:space="preserve">cheptais</t>
   </si>
   <si>
+    <t xml:space="preserve">1.99 (1.46-2.71)</t>
+  </si>
+  <si>
     <t xml:space="preserve">turbo</t>
   </si>
   <si>
     <t xml:space="preserve">nyatike</t>
   </si>
   <si>
-    <t xml:space="preserve">Elgeyo Marakwet </t>
+    <t xml:space="preserve">1.99 (1.47-2.69)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elgeyo Marakwet</t>
   </si>
   <si>
     <t xml:space="preserve">keiyo north</t>
@@ -134,51 +155,66 @@
     <t xml:space="preserve">alego usonga</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trans Nzoia </t>
+    <t xml:space="preserve">1.98 (1.47-2.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trans Nzoia</t>
   </si>
   <si>
     <t xml:space="preserve">cherangany</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilifi </t>
+    <t xml:space="preserve">1.98 (1.47-2.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kilifi</t>
   </si>
   <si>
     <t xml:space="preserve">kilifi south</t>
   </si>
   <si>
-    <t xml:space="preserve">Nairobi </t>
+    <t xml:space="preserve">1.98 (1.46-2.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nairobi</t>
   </si>
   <si>
     <t xml:space="preserve">westlands</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97</t>
+    <t xml:space="preserve">1.97 (1.46-2.67)</t>
   </si>
   <si>
     <t xml:space="preserve">saboti</t>
   </si>
   <si>
+    <t xml:space="preserve">1.97 (1.46-2.65)</t>
+  </si>
+  <si>
     <t xml:space="preserve">malava</t>
   </si>
   <si>
-    <t xml:space="preserve">Kericho </t>
+    <t xml:space="preserve">1.97 (1.47-2.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kericho</t>
   </si>
   <si>
     <t xml:space="preserve">buret</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakuru </t>
+    <t xml:space="preserve">1.96 (1.46-2.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakuru</t>
   </si>
   <si>
     <t xml:space="preserve">nakuru town west</t>
   </si>
   <si>
+    <t xml:space="preserve">1.96 (1.46-2.64)</t>
+  </si>
+  <si>
     <t xml:space="preserve">suna east</t>
   </si>
   <si>
@@ -188,72 +224,96 @@
     <t xml:space="preserve">molo</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95</t>
+    <t xml:space="preserve">1.95 (1.45-2.63)</t>
   </si>
   <si>
     <t xml:space="preserve">matungu</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95 (1.46-2.62)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kadibo</t>
   </si>
   <si>
     <t xml:space="preserve">butula</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui </t>
+    <t xml:space="preserve">Kitui</t>
   </si>
   <si>
     <t xml:space="preserve">kitui west</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95 (1.45-2.62)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kasarani</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana </t>
+    <t xml:space="preserve">Turkana</t>
   </si>
   <si>
     <t xml:space="preserve">lokichoggio</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomet </t>
+    <t xml:space="preserve">1.95 (1.44-2.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomet</t>
   </si>
   <si>
     <t xml:space="preserve">sotik</t>
   </si>
   <si>
+    <t xml:space="preserve">1.95 (1.46-2.60)</t>
+  </si>
+  <si>
     <t xml:space="preserve">magarini</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homa Bay </t>
+    <t xml:space="preserve">1.94 (1.46-2.58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homa Bay</t>
   </si>
   <si>
     <t xml:space="preserve">suba south</t>
   </si>
   <si>
-    <t xml:space="preserve">Marsabit </t>
+    <t xml:space="preserve">1.94 (1.45-2.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marsabit</t>
   </si>
   <si>
     <t xml:space="preserve">north horr</t>
   </si>
   <si>
-    <t xml:space="preserve">Kisii </t>
+    <t xml:space="preserve">1.94 (1.44-2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kisii</t>
   </si>
   <si>
     <t xml:space="preserve">south mugirango</t>
   </si>
   <si>
+    <t xml:space="preserve">1.94 (1.45-2.59)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kajiado east</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93</t>
+    <t xml:space="preserve">1.93 (1.45-2.56)</t>
   </si>
   <si>
     <t xml:space="preserve">kisumu west</t>
   </si>
   <si>
+    <t xml:space="preserve">1.93 (1.45-2.57)</t>
+  </si>
+  <si>
     <t xml:space="preserve">endebess</t>
   </si>
   <si>
@@ -263,42 +323,57 @@
     <t xml:space="preserve">aroo</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92</t>
+    <t xml:space="preserve">1.92 (1.44-2.57)</t>
   </si>
   <si>
     <t xml:space="preserve">ugunja</t>
   </si>
   <si>
+    <t xml:space="preserve">1.92 (1.45-2.55)</t>
+  </si>
+  <si>
     <t xml:space="preserve">embakasi central</t>
   </si>
   <si>
-    <t xml:space="preserve">Vihiga </t>
+    <t xml:space="preserve">1.92 (1.44-2.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vihiga</t>
   </si>
   <si>
     <t xml:space="preserve">emuhaya</t>
   </si>
   <si>
-    <t xml:space="preserve">Baringo </t>
+    <t xml:space="preserve">1.92 (1.43-2.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baringo</t>
   </si>
   <si>
     <t xml:space="preserve">marigat</t>
   </si>
   <si>
+    <t xml:space="preserve">1.92 (1.44-2.54)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ruaraka</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91</t>
+    <t xml:space="preserve">1.91 (1.44-2.53)</t>
   </si>
   <si>
     <t xml:space="preserve">navakholo</t>
   </si>
   <si>
-    <t xml:space="preserve">Tharaka Nithi </t>
+    <t xml:space="preserve">Tharaka Nithi</t>
   </si>
   <si>
     <t xml:space="preserve">tharaka north</t>
   </si>
   <si>
+    <t xml:space="preserve">1.91 (1.43-2.54)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kisumu central</t>
   </si>
   <si>
@@ -308,7 +383,7 @@
     <t xml:space="preserve">kwanza</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90</t>
+    <t xml:space="preserve">1.90 (1.44-2.52)</t>
   </si>
   <si>
     <t xml:space="preserve">nakuru north</t>
@@ -320,28 +395,37 @@
     <t xml:space="preserve">changamwe</t>
   </si>
   <si>
+    <t xml:space="preserve">1.90 (1.43-2.53)</t>
+  </si>
+  <si>
     <t xml:space="preserve">rarieda</t>
   </si>
   <si>
-    <t xml:space="preserve">Taita Taveta </t>
+    <t xml:space="preserve">1.90 (1.43-2.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taita Taveta</t>
   </si>
   <si>
     <t xml:space="preserve">voi</t>
   </si>
   <si>
+    <t xml:space="preserve">1.90 (1.43-2.51)</t>
+  </si>
+  <si>
     <t xml:space="preserve">dagoretti south</t>
   </si>
   <si>
     <t xml:space="preserve">mwingi central</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89</t>
+    <t xml:space="preserve">1.89 (1.43-2.51)</t>
   </si>
   <si>
     <t xml:space="preserve">nambale</t>
   </si>
   <si>
-    <t xml:space="preserve">Nandi </t>
+    <t xml:space="preserve">Nandi</t>
   </si>
   <si>
     <t xml:space="preserve">mosop</t>
@@ -350,6 +434,9 @@
     <t xml:space="preserve">mwatate</t>
   </si>
   <si>
+    <t xml:space="preserve">1.89 (1.43-2.50)</t>
+  </si>
+  <si>
     <t xml:space="preserve">sabatia</t>
   </si>
   <si>
@@ -359,7 +446,7 @@
     <t xml:space="preserve">rachuonyo east</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga </t>
+    <t xml:space="preserve">Kirinyaga</t>
   </si>
   <si>
     <t xml:space="preserve">kirinyaga central</t>
@@ -374,21 +461,30 @@
     <t xml:space="preserve">turkana south</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88</t>
+    <t xml:space="preserve">1.88 (1.42-2.49)</t>
   </si>
   <si>
     <t xml:space="preserve">shinyalu</t>
   </si>
   <si>
+    <t xml:space="preserve">1.88 (1.43-2.48)</t>
+  </si>
+  <si>
     <t xml:space="preserve">starehe</t>
   </si>
   <si>
+    <t xml:space="preserve">1.88 (1.42-2.48)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kirinyaga east</t>
   </si>
   <si>
     <t xml:space="preserve">ainamoi</t>
   </si>
   <si>
+    <t xml:space="preserve">1.88 (1.42-2.47)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kipkelion west</t>
   </si>
   <si>
@@ -407,18 +503,27 @@
     <t xml:space="preserve">kamukunji</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87</t>
+    <t xml:space="preserve">1.87 (1.42-2.48)</t>
   </si>
   <si>
     <t xml:space="preserve">aldai</t>
   </si>
   <si>
+    <t xml:space="preserve">1.87 (1.42-2.47)</t>
+  </si>
+  <si>
     <t xml:space="preserve">embakasi south</t>
   </si>
   <si>
+    <t xml:space="preserve">1.87 (1.41-2.48)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kitutu chache north</t>
   </si>
   <si>
+    <t xml:space="preserve">1.87 (1.41-2.47)</t>
+  </si>
+  <si>
     <t xml:space="preserve">malindi</t>
   </si>
   <si>
@@ -428,7 +533,7 @@
     <t xml:space="preserve">rongo</t>
   </si>
   <si>
-    <t xml:space="preserve">Embu </t>
+    <t xml:space="preserve">Embu</t>
   </si>
   <si>
     <t xml:space="preserve">mbeere north</t>
@@ -437,15 +542,21 @@
     <t xml:space="preserve">vihiga</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86</t>
+    <t xml:space="preserve">1.86 (1.41-2.47)</t>
   </si>
   <si>
     <t xml:space="preserve">kitutu chache south</t>
   </si>
   <si>
+    <t xml:space="preserve">1.86 (1.41-2.45)</t>
+  </si>
+  <si>
     <t xml:space="preserve">nyaribari chache</t>
   </si>
   <si>
+    <t xml:space="preserve">1.86 (1.41-2.46)</t>
+  </si>
+  <si>
     <t xml:space="preserve">nyando</t>
   </si>
   <si>
@@ -458,6 +569,9 @@
     <t xml:space="preserve">loima</t>
   </si>
   <si>
+    <t xml:space="preserve">1.86 (1.40-2.46)</t>
+  </si>
+  <si>
     <t xml:space="preserve">muhoroni</t>
   </si>
   <si>
@@ -473,7 +587,7 @@
     <t xml:space="preserve">kuria east</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyandarua </t>
+    <t xml:space="preserve">Nyandarua</t>
   </si>
   <si>
     <t xml:space="preserve">kinangop</t>
@@ -485,36 +599,48 @@
     <t xml:space="preserve">kuria west</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85</t>
+    <t xml:space="preserve">1.85 (1.41-2.44)</t>
   </si>
   <si>
     <t xml:space="preserve">tinderet</t>
   </si>
   <si>
+    <t xml:space="preserve">1.85 (1.40-2.45)</t>
+  </si>
+  <si>
     <t xml:space="preserve">likuyani</t>
   </si>
   <si>
     <t xml:space="preserve">rongai</t>
   </si>
   <si>
-    <t xml:space="preserve">Meru </t>
+    <t xml:space="preserve">1.85 (1.40-2.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meru</t>
   </si>
   <si>
     <t xml:space="preserve">tigania west</t>
   </si>
   <si>
+    <t xml:space="preserve">1.85 (1.39-2.44)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kirinyaga west</t>
   </si>
   <si>
     <t xml:space="preserve">kitui central</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84</t>
+    <t xml:space="preserve">1.84 (1.40-2.44)</t>
   </si>
   <si>
     <t xml:space="preserve">bumula</t>
   </si>
   <si>
+    <t xml:space="preserve">1.84 (1.40-2.43)</t>
+  </si>
+  <si>
     <t xml:space="preserve">nyaribari masaba</t>
   </si>
   <si>
@@ -524,9 +650,15 @@
     <t xml:space="preserve">ol kalou</t>
   </si>
   <si>
+    <t xml:space="preserve">1.84 (1.39-2.44)</t>
+  </si>
+  <si>
     <t xml:space="preserve">matungulu</t>
   </si>
   <si>
+    <t xml:space="preserve">1.84 (1.39-2.43)</t>
+  </si>
+  <si>
     <t xml:space="preserve">suba north</t>
   </si>
   <si>
@@ -536,10 +668,13 @@
     <t xml:space="preserve">turkana east</t>
   </si>
   <si>
+    <t xml:space="preserve">1.84 (1.38-2.44)</t>
+  </si>
+  <si>
     <t xml:space="preserve">nakuru town east</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83</t>
+    <t xml:space="preserve">1.83 (1.39-2.43)</t>
   </si>
   <si>
     <t xml:space="preserve">jomvu</t>
@@ -548,28 +683,37 @@
     <t xml:space="preserve">subukia</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu </t>
+    <t xml:space="preserve">Samburu</t>
   </si>
   <si>
     <t xml:space="preserve">samburu central</t>
   </si>
   <si>
+    <t xml:space="preserve">1.83 (1.38-2.42)</t>
+  </si>
+  <si>
     <t xml:space="preserve">naivasha</t>
   </si>
   <si>
+    <t xml:space="preserve">1.83 (1.38-2.41)</t>
+  </si>
+  <si>
     <t xml:space="preserve">bomachoge chache</t>
   </si>
   <si>
+    <t xml:space="preserve">1.83 (1.38-2.43)</t>
+  </si>
+  <si>
     <t xml:space="preserve">njoro</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia </t>
+    <t xml:space="preserve">Laikipia</t>
   </si>
   <si>
     <t xml:space="preserve">laikipia west</t>
   </si>
   <si>
-    <t xml:space="preserve">Kiambu </t>
+    <t xml:space="preserve">Kiambu</t>
   </si>
   <si>
     <t xml:space="preserve">githunguri</t>
@@ -578,7 +722,7 @@
     <t xml:space="preserve">turkana central</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82</t>
+    <t xml:space="preserve">1.82 (1.38-2.41)</t>
   </si>
   <si>
     <t xml:space="preserve">roysambu</t>
@@ -587,39 +731,60 @@
     <t xml:space="preserve">kikuyu</t>
   </si>
   <si>
-    <t xml:space="preserve">Makueni </t>
+    <t xml:space="preserve">1.82 (1.36-2.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Makueni</t>
   </si>
   <si>
     <t xml:space="preserve">makueni</t>
   </si>
   <si>
+    <t xml:space="preserve">1.82 (1.38-2.40)</t>
+  </si>
+  <si>
     <t xml:space="preserve">luanda</t>
   </si>
   <si>
+    <t xml:space="preserve">1.82 (1.37-2.42)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kitui rural</t>
   </si>
   <si>
+    <t xml:space="preserve">1.82 (1.37-2.41)</t>
+  </si>
+  <si>
     <t xml:space="preserve">laikipia east</t>
   </si>
   <si>
     <t xml:space="preserve">loitokitok</t>
   </si>
   <si>
+    <t xml:space="preserve">1.82 (1.37-2.40)</t>
+  </si>
+  <si>
     <t xml:space="preserve">rachuonyo north</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81</t>
+    <t xml:space="preserve">1.81 (1.37-2.40)</t>
   </si>
   <si>
     <t xml:space="preserve">samburu north</t>
   </si>
   <si>
+    <t xml:space="preserve">1.81 (1.36-2.40)</t>
+  </si>
+  <si>
     <t xml:space="preserve">gilgil</t>
   </si>
   <si>
     <t xml:space="preserve">baringo central</t>
   </si>
   <si>
+    <t xml:space="preserve">1.81 (1.36-2.41)</t>
+  </si>
+  <si>
     <t xml:space="preserve">mathare</t>
   </si>
   <si>
@@ -632,18 +797,27 @@
     <t xml:space="preserve">igembe north</t>
   </si>
   <si>
+    <t xml:space="preserve">1.81 (1.35-2.41)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ganze</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80</t>
+    <t xml:space="preserve">1.80 (1.36-2.40)</t>
   </si>
   <si>
     <t xml:space="preserve">teso south</t>
   </si>
   <si>
+    <t xml:space="preserve">1.80 (1.35-2.41)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kangundo</t>
   </si>
   <si>
+    <t xml:space="preserve">1.80 (1.35-2.40)</t>
+  </si>
+  <si>
     <t xml:space="preserve">embu north</t>
   </si>
   <si>
@@ -659,6 +833,9 @@
     <t xml:space="preserve">chepalungu</t>
   </si>
   <si>
+    <t xml:space="preserve">1.80 (1.36-2.39)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kajiado north</t>
   </si>
   <si>
@@ -668,30 +845,42 @@
     <t xml:space="preserve">chesumei</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79</t>
+    <t xml:space="preserve">1.79 (1.35-2.39)</t>
   </si>
   <si>
     <t xml:space="preserve">kalama</t>
   </si>
   <si>
+    <t xml:space="preserve">1.79 (1.34-2.40)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kisumu east</t>
   </si>
   <si>
+    <t xml:space="preserve">1.79 (1.34-2.38)</t>
+  </si>
+  <si>
     <t xml:space="preserve">rabai</t>
   </si>
   <si>
-    <t xml:space="preserve">Narok </t>
+    <t xml:space="preserve">1.79 (1.33-2.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narok</t>
   </si>
   <si>
     <t xml:space="preserve">narok central</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78</t>
+    <t xml:space="preserve">1.78 (1.34-2.37)</t>
   </si>
   <si>
     <t xml:space="preserve">kaiti</t>
   </si>
   <si>
+    <t xml:space="preserve">1.78 (1.33-2.38)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kaloleni</t>
   </si>
   <si>
@@ -707,37 +896,49 @@
     <t xml:space="preserve">mwingi west</t>
   </si>
   <si>
+    <t xml:space="preserve">1.78 (1.32-2.39)</t>
+  </si>
+  <si>
     <t xml:space="preserve">embakasi west</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77</t>
+    <t xml:space="preserve">1.77 (1.32-2.39)</t>
   </si>
   <si>
     <t xml:space="preserve">mwala</t>
   </si>
   <si>
+    <t xml:space="preserve">1.77 (1.32-2.37)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ol jorok</t>
   </si>
   <si>
+    <t xml:space="preserve">1.77 (1.31-2.39)</t>
+  </si>
+  <si>
     <t xml:space="preserve">turkana west</t>
   </si>
   <si>
     <t xml:space="preserve">samburu east</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76</t>
+    <t xml:space="preserve">1.76 (1.30-2.37)</t>
   </si>
   <si>
     <t xml:space="preserve">maara</t>
   </si>
   <si>
+    <t xml:space="preserve">1.76 (1.30-2.38)</t>
+  </si>
+  <si>
     <t xml:space="preserve">teso central</t>
   </si>
   <si>
     <t xml:space="preserve">mbeere south</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74</t>
+    <t xml:space="preserve">1.74 (1.28-2.37)</t>
   </si>
   <si>
     <t xml:space="preserve">machakos</t>
@@ -746,6 +947,9 @@
     <t xml:space="preserve">mwingi north</t>
   </si>
   <si>
+    <t xml:space="preserve">1.74 (1.28-2.36)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kabuchai</t>
   </si>
   <si>
@@ -755,43 +959,58 @@
     <t xml:space="preserve">kanduyi</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73</t>
+    <t xml:space="preserve">1.73 (1.27-2.35)</t>
   </si>
   <si>
     <t xml:space="preserve">igambangombe</t>
   </si>
   <si>
+    <t xml:space="preserve">1.73 (1.26-2.38)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kitui south</t>
   </si>
   <si>
+    <t xml:space="preserve">1.73 (1.27-2.36)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kimilili</t>
   </si>
   <si>
+    <t xml:space="preserve">1.73 (1.26-2.37)</t>
+  </si>
+  <si>
     <t xml:space="preserve">muthambi</t>
   </si>
   <si>
+    <t xml:space="preserve">1.73 (1.25-2.39)</t>
+  </si>
+  <si>
     <t xml:space="preserve">mvita</t>
   </si>
   <si>
+    <t xml:space="preserve">1.73 (1.26-2.36)</t>
+  </si>
+  <si>
     <t xml:space="preserve">kitui east</t>
   </si>
   <si>
     <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72</t>
+    <t xml:space="preserve">1.72 (1.25-2.38)</t>
   </si>
   <si>
     <t xml:space="preserve">mt. elgon</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71</t>
+    <t xml:space="preserve">1.71 (1.24-2.37)</t>
   </si>
   <si>
     <t xml:space="preserve">masinga</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70</t>
+    <t xml:space="preserve">1.70 (1.23-2.37)</t>
   </si>
 </sst>
 </file>
@@ -1173,189 +1392,189 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
         <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1363,167 +1582,167 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30">
@@ -1531,153 +1750,153 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
         <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
         <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
         <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41">
@@ -1685,27 +1904,27 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
         <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43">
@@ -1713,27 +1932,27 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45">
@@ -1741,97 +1960,97 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
@@ -1839,83 +2058,83 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C52" t="s">
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C53" t="s">
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C54" t="s">
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C57" t="s">
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
@@ -1923,307 +2142,307 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C62" t="s">
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C63" t="s">
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B65" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
         <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="C66" t="s">
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="C67" t="s">
         <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C68" t="s">
         <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="C69" t="s">
         <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
         <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
         <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
         <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
         <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
         <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="C75" t="s">
         <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
         <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B78" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
         <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s">
         <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80">
@@ -2231,167 +2450,167 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s">
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B81" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="C81" t="s">
         <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="C82" t="s">
         <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B83" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
         <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B84" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="C84" t="s">
         <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="C85" t="s">
         <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="C86" t="s">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B87" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C87" t="s">
         <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="C88" t="s">
         <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="C89" t="s">
         <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
         <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="C91" t="s">
         <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92">
@@ -2399,55 +2618,55 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="C92" t="s">
         <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B93" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="C94" t="s">
         <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="C95" t="s">
         <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96">
@@ -2455,251 +2674,251 @@
         <v>4</v>
       </c>
       <c r="B96" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="C96" t="s">
         <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="C97" t="s">
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
         <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B99" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
         <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B100" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="C100" t="s">
         <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B101" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="C101" t="s">
         <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="C102" t="s">
         <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>141</v>
+        <v>178</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
         <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B104" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="C104" t="s">
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="C105" t="s">
         <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B106" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s">
         <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="B107" t="s">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="C107" t="s">
         <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B108" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="C108" t="s">
         <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B109" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="C109" t="s">
         <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B110" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="C110" t="s">
         <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B111" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="C111" t="s">
         <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B112" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="C112" t="s">
         <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B113" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C113" t="s">
         <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114">
@@ -2707,433 +2926,433 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="C114" t="s">
         <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B115" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="C115" t="s">
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="C116" t="s">
         <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B117" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="C117" t="s">
         <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="C118" t="s">
         <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B119" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s">
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="C120" t="s">
         <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="B121" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="C121" t="s">
         <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c r="C122" t="s">
         <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B123" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="C123" t="s">
         <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>175</v>
+        <v>229</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="C124" t="s">
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="B125" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="C125" t="s">
         <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B126" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="C126" t="s">
         <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B127" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
         <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B128" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="C128" t="s">
         <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B129" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="C129" t="s">
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="B130" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="C130" t="s">
         <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B131" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="C131" t="s">
         <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>188</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B132" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
       <c r="C132" t="s">
         <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="B133" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
       <c r="C133" t="s">
         <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B134" t="s">
-        <v>196</v>
+        <v>248</v>
       </c>
       <c r="C134" t="s">
         <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B135" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="C135" t="s">
         <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="B136" t="s">
-        <v>199</v>
+        <v>252</v>
       </c>
       <c r="C136" t="s">
         <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="C137" t="s">
         <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B138" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="C138" t="s">
         <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B139" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="C139" t="s">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B140" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="C140" t="s">
         <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B141" t="s">
-        <v>204</v>
+        <v>259</v>
       </c>
       <c r="C141" t="s">
         <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="B142" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="C142" t="s">
         <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>198</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B143" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="C143" t="s">
         <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B144" t="s">
-        <v>208</v>
+        <v>264</v>
       </c>
       <c r="C144" t="s">
         <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>207</v>
+        <v>265</v>
       </c>
     </row>
     <row r="145">
@@ -3141,125 +3360,125 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="C145" t="s">
         <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B146" t="s">
-        <v>210</v>
+        <v>268</v>
       </c>
       <c r="C146" t="s">
         <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B147" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="C147" t="s">
         <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>212</v>
+        <v>270</v>
       </c>
       <c r="C148" t="s">
         <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B149" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="C149" t="s">
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B150" t="s">
-        <v>214</v>
+        <v>272</v>
       </c>
       <c r="C150" t="s">
         <v>6</v>
       </c>
       <c r="D150" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B151" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C151" t="s">
         <v>6</v>
       </c>
       <c r="D151" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="B152" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C152" t="s">
         <v>6</v>
       </c>
       <c r="D152" t="s">
-        <v>207</v>
+        <v>267</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B153" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="C153" t="s">
         <v>6</v>
       </c>
       <c r="D153" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
     </row>
     <row r="154">
@@ -3267,13 +3486,13 @@
         <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="C154" t="s">
         <v>6</v>
       </c>
       <c r="D154" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
     </row>
     <row r="155">
@@ -3281,69 +3500,69 @@
         <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="C155" t="s">
         <v>6</v>
       </c>
       <c r="D155" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B156" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="C156" t="s">
         <v>6</v>
       </c>
       <c r="D156" t="s">
-        <v>218</v>
+        <v>283</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="B157" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="C157" t="s">
         <v>6</v>
       </c>
       <c r="D157" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="B158" t="s">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="C158" t="s">
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B159" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
       <c r="C159" t="s">
         <v>6</v>
       </c>
       <c r="D159" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="160">
@@ -3351,69 +3570,69 @@
         <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>227</v>
+        <v>290</v>
       </c>
       <c r="C160" t="s">
         <v>6</v>
       </c>
       <c r="D160" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="B161" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="C161" t="s">
         <v>6</v>
       </c>
       <c r="D161" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B162" t="s">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="C162" t="s">
         <v>6</v>
       </c>
       <c r="D162" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B163" t="s">
-        <v>230</v>
+        <v>293</v>
       </c>
       <c r="C163" t="s">
         <v>6</v>
       </c>
       <c r="D163" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B164" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="C164" t="s">
         <v>6</v>
       </c>
       <c r="D164" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
     </row>
     <row r="165">
@@ -3421,97 +3640,97 @@
         <v>11</v>
       </c>
       <c r="B165" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="C165" t="s">
         <v>6</v>
       </c>
       <c r="D165" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B166" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="C166" t="s">
         <v>6</v>
       </c>
       <c r="D166" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B167" t="s">
-        <v>235</v>
+        <v>301</v>
       </c>
       <c r="C167" t="s">
         <v>6</v>
       </c>
       <c r="D167" t="s">
-        <v>232</v>
+        <v>300</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="B168" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="C168" t="s">
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>237</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B169" t="s">
-        <v>238</v>
+        <v>304</v>
       </c>
       <c r="C169" t="s">
         <v>6</v>
       </c>
       <c r="D169" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B170" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="C170" t="s">
         <v>6</v>
       </c>
       <c r="D170" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="B171" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="C171" t="s">
         <v>6</v>
       </c>
       <c r="D171" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
     </row>
     <row r="172">
@@ -3519,181 +3738,181 @@
         <v>11</v>
       </c>
       <c r="B172" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="C172" t="s">
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B173" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="C173" t="s">
         <v>6</v>
       </c>
       <c r="D173" t="s">
-        <v>241</v>
+        <v>311</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B174" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="C174" t="s">
         <v>6</v>
       </c>
       <c r="D174" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="B175" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C175" t="s">
         <v>6</v>
       </c>
       <c r="D175" t="s">
-        <v>241</v>
+        <v>311</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B176" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="C176" t="s">
         <v>6</v>
       </c>
       <c r="D176" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B177" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="C177" t="s">
         <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>247</v>
+        <v>317</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B178" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="C178" t="s">
         <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B179" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
       <c r="C179" t="s">
         <v>6</v>
       </c>
       <c r="D179" t="s">
-        <v>247</v>
+        <v>321</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B180" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
       <c r="C180" t="s">
         <v>6</v>
       </c>
       <c r="D180" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B181" t="s">
-        <v>252</v>
+        <v>324</v>
       </c>
       <c r="C181" t="s">
         <v>6</v>
       </c>
       <c r="D181" t="s">
-        <v>247</v>
+        <v>325</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B182" t="s">
-        <v>253</v>
+        <v>326</v>
       </c>
       <c r="C182" t="s">
         <v>6</v>
       </c>
       <c r="D182" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B183" t="s">
-        <v>254</v>
+        <v>327</v>
       </c>
       <c r="C183" t="s">
         <v>6</v>
       </c>
       <c r="D183" t="s">
-        <v>255</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B184" t="s">
-        <v>256</v>
+        <v>329</v>
       </c>
       <c r="C184" t="s">
         <v>6</v>
       </c>
       <c r="D184" t="s">
-        <v>257</v>
+        <v>330</v>
       </c>
     </row>
     <row r="185">
@@ -3701,13 +3920,13 @@
         <v>11</v>
       </c>
       <c r="B185" t="s">
-        <v>258</v>
+        <v>331</v>
       </c>
       <c r="C185" t="s">
         <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
